--- a/data/trans_orig/P3A$yo-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P3A$yo-Habitat-trans_orig.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W54"/>
+  <dimension ref="A1:W39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según quién se ocupa principalmente de las tareas domésticas (multirrespuesta) en 2023</t>
+          <t>Hogares según quién se ocupa principalmente de las tareas domésticas (multirrespuesta) en 2023 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>372385</t>
+          <t>371840</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>427817</t>
+          <t>428157</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>58,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>67,38%</t>
+          <t>67,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>667438</t>
+          <t>666884</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>692558</t>
+          <t>692062</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1043579</t>
+          <t>1043492</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1121855</t>
+          <t>1118120</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>76,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>82,2%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>262779</t>
+          <t>260394</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>318501</t>
+          <t>318264</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,16%</t>
+          <t>50,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>118536</t>
+          <t>118851</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>172984</t>
+          <t>171940</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>390554</t>
+          <t>380843</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>480274</t>
+          <t>480453</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>35,32%</t>
         </is>
       </c>
     </row>
@@ -941,112 +941,112 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Mi pareja y yo</t>
+          <t>Otra persona del hogar</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>151</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>165961</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>140079</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1670</t>
+          <t>199580</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>246</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>200082</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>156112</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1122</t>
+          <t>312227</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>43,05%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>397</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>366043</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>313766</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1325</t>
+          <t>498509</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>36,65%</t>
         </is>
       </c>
     </row>
@@ -1054,112 +1054,112 @@
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Otra persona que no es mi pareja y yo</t>
+          <t>Otra persona que no reside en el hogar y no esta contratada (familiares/vecinos/amigos)</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31708</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23464</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1670</t>
+          <t>41767</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>87</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>35315</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>26694</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1122</t>
+          <t>44214</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>138</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>67024</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>53805</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1325</t>
+          <t>79050</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>5,81%</t>
         </is>
       </c>
     </row>
@@ -1167,112 +1167,112 @@
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Otra persona del hogar</t>
+          <t>Otra persona que no reside en el hogar y que cobra de los ingresos del hogar</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>165961</t>
+          <t>21042</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>139276</t>
+          <t>14090</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>194561</t>
+          <t>29883</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>53</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>200082</t>
+          <t>23445</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>155237</t>
+          <t>16604</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>320522</t>
+          <t>31261</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>85</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>366043</t>
+          <t>44486</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>310496</t>
+          <t>34936</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>488023</t>
+          <t>57067</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -1280,112 +1280,112 @@
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Una persona contratada para ello</t>
+          <t>Otra persona que no reside en el hogar y que sí cobra aunque no de los ingresos del hogar</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19695</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13185</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1670</t>
+          <t>28375</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>66</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25311</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18468</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1122</t>
+          <t>32182</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>96</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45006</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>35831</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1325</t>
+          <t>55863</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -1393,225 +1393,229 @@
       <c r="A10" s="1" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Otra persona que no reside en el hogar y no esta contratada (familiares/vecinos/amigos)</t>
+          <t>Otra situación</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>31708</t>
+          <t>1465</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23935</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42577</t>
+          <t>7853</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>35315</t>
+          <t>379</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27506</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44601</t>
+          <t>1774</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>67024</t>
+          <t>1844</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>55648</t>
+          <t>170</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>81021</t>
+          <t>8291</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>0,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>0,61%</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n"/>
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Otra persona que no reside en el hogar y que cobra de los ingresos del hogar</t>
+          <t>Yo</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>624</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21042</t>
+          <t>619109</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14019</t>
+          <t>296623</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29750</t>
+          <t>791176</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>51,9%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>66,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>1411</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>23445</t>
+          <t>883438</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17050</t>
+          <t>865503</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30791</t>
+          <t>898428</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>2035</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>44486</t>
+          <t>1502548</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>34487</t>
+          <t>1017286</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>55266</t>
+          <t>1708633</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>69,84%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>47,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>79,42%</t>
         </is>
       </c>
     </row>
@@ -1619,112 +1623,112 @@
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Otra persona que no reside en el hogar y que sí cobra aunque no de los ingresos del hogar</t>
+          <t>Mi pareja</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>527</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>19695</t>
+          <t>473828</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13219</t>
+          <t>237376</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>29055</t>
+          <t>609670</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>51,11%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>362</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>25311</t>
+          <t>239285</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>19146</t>
+          <t>217128</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>32586</t>
+          <t>262583</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>889</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>45006</t>
+          <t>713113</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>34668</t>
+          <t>478250</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>55043</t>
+          <t>816366</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>37,94%</t>
         </is>
       </c>
     </row>
@@ -1732,229 +1736,225 @@
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Otra situación</t>
+          <t>Otra persona del hogar</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>224</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1465</t>
+          <t>271931</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>133360</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7614</t>
+          <t>358109</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>341</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>244987</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>220884</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2068</t>
+          <t>271239</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>565</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1844</t>
+          <t>516918</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>338625</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7893</t>
+          <t>599304</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>27,85%</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>10-50.000 hab</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Yo</t>
+          <t>Otra persona que no reside en el hogar y no esta contratada (familiares/vecinos/amigos)</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>45</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>619109</t>
+          <t>28431</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>333978</t>
+          <t>14727</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>793333</t>
+          <t>41613</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>51,9%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1411</t>
+          <t>88</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>883438</t>
+          <t>43839</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>864063</t>
+          <t>34542</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>898875</t>
+          <t>54215</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>2035</t>
+          <t>133</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1502548</t>
+          <t>72271</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1023615</t>
+          <t>47881</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1708519</t>
+          <t>88892</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>69,84%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,41%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -1962,112 +1962,112 @@
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Mi pareja</t>
+          <t>Otra persona que no reside en el hogar y que cobra de los ingresos del hogar</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>473828</t>
+          <t>19973</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>262095</t>
+          <t>9046</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>610232</t>
+          <t>35732</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>239285</t>
+          <t>26954</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>216020</t>
+          <t>19848</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>262738</t>
+          <t>35752</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>889</t>
+          <t>75</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>713113</t>
+          <t>46927</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>486966</t>
+          <t>30599</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>816404</t>
+          <t>63357</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -2075,112 +2075,112 @@
       <c r="A16" s="1" t="n"/>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Mi pareja y yo</t>
+          <t>Otra persona que no reside en el hogar y que sí cobra aunque no de los ingresos del hogar</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17022</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8318</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2374</t>
+          <t>28359</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25699</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18826</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1213</t>
+          <t>34290</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>72</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>42722</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>27551</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1665</t>
+          <t>55928</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -2188,225 +2188,229 @@
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Otra persona que no es mi pareja y yo</t>
+          <t>Otra situación</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>255764</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10760</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2374</t>
+          <t>736657</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>61,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7281</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3546</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1213</t>
+          <t>14347</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>263046</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17481</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1665</t>
+          <t>859721</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>39,96%</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n"/>
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Otra persona del hogar</t>
+          <t>Yo</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>461</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>271931</t>
+          <t>477663</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>147634</t>
+          <t>447112</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>355378</t>
+          <t>507257</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>67,78%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>63,45%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>71,98%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>972</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>244987</t>
+          <t>870118</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>218949</t>
+          <t>842797</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>270061</t>
+          <t>904586</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>1433</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>516918</t>
+          <t>1347781</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>352319</t>
+          <t>1289041</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>598213</t>
+          <t>1445410</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>78,69%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>88,24%</t>
         </is>
       </c>
     </row>
@@ -2414,112 +2418,112 @@
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Una persona contratada para ello</t>
+          <t>Mi pareja</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>376</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>354950</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>325665</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2374</t>
+          <t>387721</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,37%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>46,21%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>55,02%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>257</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>173422</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>88730</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1213</t>
+          <t>232674</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>528372</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>359697</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1665</t>
+          <t>622696</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>38,01%</t>
         </is>
       </c>
     </row>
@@ -2527,112 +2531,112 @@
       <c r="A20" s="1" t="n"/>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Otra persona que no reside en el hogar y no esta contratada (familiares/vecinos/amigos)</t>
+          <t>Otra persona del hogar</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>169</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>28431</t>
+          <t>223641</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>14093</t>
+          <t>194309</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>41055</t>
+          <t>259888</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>235</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>43839</t>
+          <t>195372</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>35743</t>
+          <t>92286</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>54127</t>
+          <t>264913</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>404</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>72271</t>
+          <t>419013</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>46585</t>
+          <t>277478</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>88490</t>
+          <t>497298</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>30,36%</t>
         </is>
       </c>
     </row>
@@ -2640,112 +2644,112 @@
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Otra persona que no reside en el hogar y que cobra de los ingresos del hogar</t>
+          <t>Otra persona que no reside en el hogar y no esta contratada (familiares/vecinos/amigos)</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>19973</t>
+          <t>16890</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9649</t>
+          <t>10473</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>35689</t>
+          <t>26668</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>58</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>26954</t>
+          <t>34121</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>19871</t>
+          <t>16121</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>35865</t>
+          <t>48787</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>78</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>46927</t>
+          <t>51011</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>31243</t>
+          <t>32282</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>62173</t>
+          <t>65660</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -2753,112 +2757,112 @@
       <c r="A22" s="1" t="n"/>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Otra persona que no reside en el hogar y que sí cobra aunque no de los ingresos del hogar</t>
+          <t>Otra persona que no reside en el hogar y que cobra de los ingresos del hogar</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>17022</t>
+          <t>18225</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7283</t>
+          <t>10887</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29841</t>
+          <t>29511</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>25699</t>
+          <t>25085</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>18882</t>
+          <t>10688</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>34983</t>
+          <t>36396</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>65</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>42722</t>
+          <t>43310</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>29304</t>
+          <t>27824</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>59381</t>
+          <t>57793</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2870,7 @@
       <c r="A23" s="1" t="n"/>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Otra situación</t>
+          <t>Otra persona que no reside en el hogar y que sí cobra aunque no de los ingresos del hogar</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2876,332 +2880,332 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>255764</t>
+          <t>9085</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>11645</t>
+          <t>4733</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>680853</t>
+          <t>15781</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>57,08%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>7281</t>
+          <t>10491</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3362</t>
+          <t>4648</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>14536</t>
+          <t>17377</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>31</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>263046</t>
+          <t>19576</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>18636</t>
+          <t>11354</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>858908</t>
+          <t>29913</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A24" s="1" t="n"/>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Yo</t>
+          <t>Otra situación</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>477663</t>
+          <t>3967</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>448385</t>
+          <t>1167</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>507459</t>
+          <t>9298</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>63,63%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>870118</t>
+          <t>3988</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>839449</t>
+          <t>1032</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>899971</t>
+          <t>13615</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>1433</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1347781</t>
+          <t>7955</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1291978</t>
+          <t>3435</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1447117</t>
+          <t>17631</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n"/>
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Mi pareja</t>
+          <t>Yo</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>667</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>354950</t>
+          <t>622054</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>321269</t>
+          <t>588974</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>384811</t>
+          <t>652798</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>50,37%</t>
+          <t>67,16%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>45,59%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>70,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>1402</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>173422</t>
+          <t>963142</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>95578</t>
+          <t>935813</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>233692</t>
+          <t>990670</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>2069</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>528372</t>
+          <t>1585195</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>357419</t>
+          <t>1542309</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>618868</t>
+          <t>1643001</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>76,36%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>81,34%</t>
         </is>
       </c>
     </row>
@@ -3209,112 +3213,112 @@
       <c r="A26" s="1" t="n"/>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Mi pareja y yo</t>
+          <t>Mi pareja</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>522</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>437081</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>405121</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1999</t>
+          <t>471841</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>50,94%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>314</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>200961</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>161415</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1710</t>
+          <t>227891</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>836</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>638042</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>562910</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1825</t>
+          <t>682187</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>33,77%</t>
         </is>
       </c>
     </row>
@@ -3322,112 +3326,112 @@
       <c r="A27" s="1" t="n"/>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Otra persona que no es mi pareja y yo</t>
+          <t>Otra persona del hogar</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>211</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>248825</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>213908</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1999</t>
+          <t>278676</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>333</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>262617</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>209021</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1710</t>
+          <t>296202</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>544</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>511441</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>446983</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1825</t>
+          <t>560134</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>27,73%</t>
         </is>
       </c>
     </row>
@@ -3435,112 +3439,112 @@
       <c r="A28" s="1" t="n"/>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Otra persona del hogar</t>
+          <t>Otra persona que no reside en el hogar y no esta contratada (familiares/vecinos/amigos)</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>223641</t>
+          <t>28096</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>193273</t>
+          <t>18740</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>256157</t>
+          <t>49501</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>65</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>195372</t>
+          <t>33565</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>110132</t>
+          <t>25251</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>266032</t>
+          <t>43285</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>97</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>419013</t>
+          <t>61660</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>275840</t>
+          <t>49100</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>491415</t>
+          <t>81914</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -3548,112 +3552,112 @@
       <c r="A29" s="1" t="n"/>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Una persona contratada para ello</t>
+          <t>Otra persona que no reside en el hogar y que cobra de los ingresos del hogar</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>35971</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25793</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1999</t>
+          <t>49549</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>80</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48401</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>36784</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1710</t>
+          <t>62019</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>125</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>84372</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>69106</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1825</t>
+          <t>103050</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -3661,112 +3665,112 @@
       <c r="A30" s="1" t="n"/>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Otra persona que no reside en el hogar y no esta contratada (familiares/vecinos/amigos)</t>
+          <t>Otra persona que no reside en el hogar y que sí cobra aunque no de los ingresos del hogar</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>16890</t>
+          <t>11705</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>10265</t>
+          <t>6999</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>25346</t>
+          <t>18597</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>34121</t>
+          <t>21011</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>17501</t>
+          <t>14759</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>49344</t>
+          <t>29340</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>56</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>51011</t>
+          <t>32716</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>32865</t>
+          <t>24040</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>65667</t>
+          <t>42587</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -3774,225 +3778,229 @@
       <c r="A31" s="1" t="n"/>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Otra persona que no reside en el hogar y que cobra de los ingresos del hogar</t>
+          <t>Otra situación</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>18225</t>
+          <t>16224</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>11498</t>
+          <t>8433</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>31187</t>
+          <t>32885</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>25085</t>
+          <t>14946</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>12801</t>
+          <t>8761</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>37098</t>
+          <t>28513</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>30</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>43310</t>
+          <t>31170</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>27850</t>
+          <t>19483</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>58543</t>
+          <t>47112</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n"/>
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Otra persona que no reside en el hogar y que sí cobra aunque no de los ingresos del hogar</t>
+          <t>Yo</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2227</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>9085</t>
+          <t>2120608</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>4878</t>
+          <t>1616269</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>15854</t>
+          <t>2302431</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>61,31%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>46,73%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>66,57%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>4937</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>10491</t>
+          <t>3397577</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>4736</t>
+          <t>3353826</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>17333</t>
+          <t>3455773</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>7164</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>19576</t>
+          <t>5518185</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>11922</t>
+          <t>4883769</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>29617</t>
+          <t>5758566</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>76,96%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>68,12%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>80,32%</t>
         </is>
       </c>
     </row>
@@ -4000,229 +4008,225 @@
       <c r="A33" s="1" t="n"/>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Otra situación</t>
+          <t>Mi pareja</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>3967</t>
+          <t>1554951</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1162</t>
+          <t>1192592</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>9689</t>
+          <t>1700703</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>49,17%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1206</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>3988</t>
+          <t>765770</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>614292</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>13764</t>
+          <t>843229</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2979</t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>7955</t>
+          <t>2320721</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>3698</t>
+          <t>2016671</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>17029</t>
+          <t>2492035</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>34,76%</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>Capitales</t>
-        </is>
-      </c>
+      <c r="A34" s="1" t="n"/>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Yo</t>
+          <t>Otra persona del hogar</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>755</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>622054</t>
+          <t>910358</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>590454</t>
+          <t>712530</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>653645</t>
+          <t>1001359</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>1402</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>963142</t>
+          <t>903057</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>938175</t>
+          <t>737230</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>993110</t>
+          <t>1025692</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>2069</t>
+          <t>1910</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>1585195</t>
+          <t>1813415</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1540611</t>
+          <t>1611652</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1642909</t>
+          <t>1974983</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>78,48%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>81,34%</t>
+          <t>27,55%</t>
         </is>
       </c>
     </row>
@@ -4230,112 +4234,112 @@
       <c r="A35" s="1" t="n"/>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Mi pareja</t>
+          <t>Otra persona que no reside en el hogar y no esta contratada (familiares/vecinos/amigos)</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>148</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>437081</t>
+          <t>105125</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>402490</t>
+          <t>79067</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>470256</t>
+          <t>129235</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>298</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>200961</t>
+          <t>146841</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>161555</t>
+          <t>117353</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>227602</t>
+          <t>167125</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>836</t>
+          <t>446</t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>638042</t>
+          <t>251965</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>570215</t>
+          <t>209298</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>681340</t>
+          <t>283026</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -4343,112 +4347,112 @@
       <c r="A36" s="1" t="n"/>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Mi pareja y yo</t>
+          <t>Otra persona que no reside en el hogar y que cobra de los ingresos del hogar</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>123</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>95211</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>72969</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>1768</t>
+          <t>117979</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>227</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>123885</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>99331</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1346</t>
+          <t>143985</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>350</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>219096</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>186252</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1512</t>
+          <t>253087</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -4456,112 +4460,112 @@
       <c r="A37" s="1" t="n"/>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Otra persona que no es mi pareja y yo</t>
+          <t>Otra persona que no reside en el hogar y que sí cobra aunque no de los ingresos del hogar</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>81</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>57508</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>42948</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1768</t>
+          <t>74293</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>174</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>82512</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>67461</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>1346</t>
+          <t>98508</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>255</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>140020</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>118415</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1512</t>
+          <t>162345</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -4569,1816 +4573,117 @@
       <c r="A38" s="1" t="n"/>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Otra persona del hogar</t>
+          <t>Otra situación</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>248825</t>
+          <t>277420</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>217149</t>
+          <t>30528</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>282407</t>
+          <t>1057929</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>262617</t>
+          <t>26594</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>207075</t>
+          <t>16841</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>295608</t>
+          <t>40858</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>67</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>511441</t>
+          <t>304014</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>453932</t>
+          <t>54832</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>561838</t>
+          <t>1050624</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>14,65%</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n"/>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>Una persona contratada para ello</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>1768</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>1346</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O39" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P39" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
-      <c r="Q39" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R39" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S39" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T39" s="2" t="inlineStr">
-        <is>
-          <t>1512</t>
-        </is>
-      </c>
-      <c r="U39" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="V39" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="W39" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="n"/>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>Otra persona que no reside en el hogar y no esta contratada (familiares/vecinos/amigos)</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>28096</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>18475</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>49447</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>3,03%</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>1,99%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>5,34%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>33565</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>25270</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>42763</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>3,07%</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>2,31%</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>3,91%</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>61660</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t>48819</t>
-        </is>
-      </c>
-      <c r="T40" s="2" t="inlineStr">
-        <is>
-          <t>84083</t>
-        </is>
-      </c>
-      <c r="U40" s="2" t="inlineStr">
-        <is>
-          <t>3,05%</t>
-        </is>
-      </c>
-      <c r="V40" s="2" t="inlineStr">
-        <is>
-          <t>2,42%</t>
-        </is>
-      </c>
-      <c r="W40" s="2" t="inlineStr">
-        <is>
-          <t>4,16%</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="n"/>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>Otra persona que no reside en el hogar y que cobra de los ingresos del hogar</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>35971</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>26241</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>50014</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>3,88%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>2,83%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>5,4%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>48401</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>36635</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>60748</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>4,43%</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>3,35%</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>5,55%</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>84372</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>68868</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
-          <t>101262</t>
-        </is>
-      </c>
-      <c r="U41" s="2" t="inlineStr">
-        <is>
-          <t>4,18%</t>
-        </is>
-      </c>
-      <c r="V41" s="2" t="inlineStr">
-        <is>
-          <t>3,41%</t>
-        </is>
-      </c>
-      <c r="W41" s="2" t="inlineStr">
-        <is>
-          <t>5,01%</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="n"/>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>Otra persona que no reside en el hogar y que sí cobra aunque no de los ingresos del hogar</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>11705</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>7080</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>19053</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>2,06%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>21011</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>14708</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>29172</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>1,92%</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>2,67%</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t>32716</t>
-        </is>
-      </c>
-      <c r="S42" s="2" t="inlineStr">
-        <is>
-          <t>24671</t>
-        </is>
-      </c>
-      <c r="T42" s="2" t="inlineStr">
-        <is>
-          <t>41898</t>
-        </is>
-      </c>
-      <c r="U42" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
-      <c r="V42" s="2" t="inlineStr">
-        <is>
-          <t>1,22%</t>
-        </is>
-      </c>
-      <c r="W42" s="2" t="inlineStr">
-        <is>
-          <t>2,07%</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="n"/>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>Otra situación</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>16224</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>8950</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>32813</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>1,75%</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>3,54%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>14946</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>8194</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>26860</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>1,37%</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t>31170</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t>20716</t>
-        </is>
-      </c>
-      <c r="T43" s="2" t="inlineStr">
-        <is>
-          <t>49573</t>
-        </is>
-      </c>
-      <c r="U43" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
-      <c r="V43" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
-      <c r="W43" s="2" t="inlineStr">
-        <is>
-          <t>2,45%</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>Yo</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>2227</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>2120608</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>1645467</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>2299797</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>61,31%</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>47,57%</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>66,49%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>4937</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>3397577</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>3352739</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>3457073</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>91,55%</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>90,35%</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>93,16%</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t>7164</t>
-        </is>
-      </c>
-      <c r="R44" s="2" t="inlineStr">
-        <is>
-          <t>5518185</t>
-        </is>
-      </c>
-      <c r="S44" s="2" t="inlineStr">
-        <is>
-          <t>4804174</t>
-        </is>
-      </c>
-      <c r="T44" s="2" t="inlineStr">
-        <is>
-          <t>5760368</t>
-        </is>
-      </c>
-      <c r="U44" s="2" t="inlineStr">
-        <is>
-          <t>76,96%</t>
-        </is>
-      </c>
-      <c r="V44" s="2" t="inlineStr">
-        <is>
-          <t>67,01%</t>
-        </is>
-      </c>
-      <c r="W44" s="2" t="inlineStr">
-        <is>
-          <t>80,34%</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="n"/>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>Mi pareja</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>1773</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>1554951</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>1208113</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>1697451</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>44,96%</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>34,93%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>49,08%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>1206</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>765770</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>627449</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>836915</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr">
-        <is>
-          <t>20,64%</t>
-        </is>
-      </c>
-      <c r="O45" s="2" t="inlineStr">
-        <is>
-          <t>16,91%</t>
-        </is>
-      </c>
-      <c r="P45" s="2" t="inlineStr">
-        <is>
-          <t>22,55%</t>
-        </is>
-      </c>
-      <c r="Q45" s="2" t="inlineStr">
-        <is>
-          <t>2979</t>
-        </is>
-      </c>
-      <c r="R45" s="2" t="inlineStr">
-        <is>
-          <t>2320721</t>
-        </is>
-      </c>
-      <c r="S45" s="2" t="inlineStr">
-        <is>
-          <t>2013590</t>
-        </is>
-      </c>
-      <c r="T45" s="2" t="inlineStr">
-        <is>
-          <t>2495759</t>
-        </is>
-      </c>
-      <c r="U45" s="2" t="inlineStr">
-        <is>
-          <t>32,37%</t>
-        </is>
-      </c>
-      <c r="V45" s="2" t="inlineStr">
-        <is>
-          <t>28,08%</t>
-        </is>
-      </c>
-      <c r="W45" s="2" t="inlineStr">
-        <is>
-          <t>34,81%</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="n"/>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>Mi pareja y yo</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>1968</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>1328</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O46" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P46" s="2" t="inlineStr">
-        <is>
-          <t>0,04%</t>
-        </is>
-      </c>
-      <c r="Q46" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R46" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S46" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T46" s="2" t="inlineStr">
-        <is>
-          <t>1576</t>
-        </is>
-      </c>
-      <c r="U46" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="V46" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="W46" s="2" t="inlineStr">
-        <is>
-          <t>0,02%</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="n"/>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>Otra persona que no es mi pareja y yo</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>1968</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr">
-        <is>
-          <t>1328</t>
-        </is>
-      </c>
-      <c r="N47" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O47" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P47" s="2" t="inlineStr">
-        <is>
-          <t>0,04%</t>
-        </is>
-      </c>
-      <c r="Q47" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R47" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S47" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T47" s="2" t="inlineStr">
-        <is>
-          <t>1576</t>
-        </is>
-      </c>
-      <c r="U47" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="V47" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="W47" s="2" t="inlineStr">
-        <is>
-          <t>0,02%</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="n"/>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>Otra persona del hogar</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>755</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>910358</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>725812</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>1007587</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>26,32%</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>20,98%</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>29,13%</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>1155</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>903057</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="inlineStr">
-        <is>
-          <t>761999</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr">
-        <is>
-          <t>1030299</t>
-        </is>
-      </c>
-      <c r="N48" s="2" t="inlineStr">
-        <is>
-          <t>24,33%</t>
-        </is>
-      </c>
-      <c r="O48" s="2" t="inlineStr">
-        <is>
-          <t>20,53%</t>
-        </is>
-      </c>
-      <c r="P48" s="2" t="inlineStr">
-        <is>
-          <t>27,76%</t>
-        </is>
-      </c>
-      <c r="Q48" s="2" t="inlineStr">
-        <is>
-          <t>1910</t>
-        </is>
-      </c>
-      <c r="R48" s="2" t="inlineStr">
-        <is>
-          <t>1813415</t>
-        </is>
-      </c>
-      <c r="S48" s="2" t="inlineStr">
-        <is>
-          <t>1593901</t>
-        </is>
-      </c>
-      <c r="T48" s="2" t="inlineStr">
-        <is>
-          <t>1972494</t>
-        </is>
-      </c>
-      <c r="U48" s="2" t="inlineStr">
-        <is>
-          <t>25,29%</t>
-        </is>
-      </c>
-      <c r="V48" s="2" t="inlineStr">
-        <is>
-          <t>22,23%</t>
-        </is>
-      </c>
-      <c r="W48" s="2" t="inlineStr">
-        <is>
-          <t>27,51%</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="n"/>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>Una persona contratada para ello</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>1968</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr">
-        <is>
-          <t>1328</t>
-        </is>
-      </c>
-      <c r="N49" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O49" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P49" s="2" t="inlineStr">
-        <is>
-          <t>0,04%</t>
-        </is>
-      </c>
-      <c r="Q49" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R49" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S49" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T49" s="2" t="inlineStr">
-        <is>
-          <t>1576</t>
-        </is>
-      </c>
-      <c r="U49" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="V49" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="W49" s="2" t="inlineStr">
-        <is>
-          <t>0,02%</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="n"/>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>Otra persona que no reside en el hogar y no esta contratada (familiares/vecinos/amigos)</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>105125</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>80790</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>130554</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>3,04%</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>2,34%</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>3,77%</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>298</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>146841</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="inlineStr">
-        <is>
-          <t>118675</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr">
-        <is>
-          <t>165885</t>
-        </is>
-      </c>
-      <c r="N50" s="2" t="inlineStr">
-        <is>
-          <t>3,96%</t>
-        </is>
-      </c>
-      <c r="O50" s="2" t="inlineStr">
-        <is>
-          <t>3,2%</t>
-        </is>
-      </c>
-      <c r="P50" s="2" t="inlineStr">
-        <is>
-          <t>4,47%</t>
-        </is>
-      </c>
-      <c r="Q50" s="2" t="inlineStr">
-        <is>
-          <t>446</t>
-        </is>
-      </c>
-      <c r="R50" s="2" t="inlineStr">
-        <is>
-          <t>251965</t>
-        </is>
-      </c>
-      <c r="S50" s="2" t="inlineStr">
-        <is>
-          <t>219839</t>
-        </is>
-      </c>
-      <c r="T50" s="2" t="inlineStr">
-        <is>
-          <t>285265</t>
-        </is>
-      </c>
-      <c r="U50" s="2" t="inlineStr">
-        <is>
-          <t>3,51%</t>
-        </is>
-      </c>
-      <c r="V50" s="2" t="inlineStr">
-        <is>
-          <t>3,07%</t>
-        </is>
-      </c>
-      <c r="W50" s="2" t="inlineStr">
-        <is>
-          <t>3,98%</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="n"/>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>Otra persona que no reside en el hogar y que cobra de los ingresos del hogar</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>95211</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>71217</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>118540</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>2,75%</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>2,06%</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>3,43%</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>123885</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr">
-        <is>
-          <t>101413</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr">
-        <is>
-          <t>142650</t>
-        </is>
-      </c>
-      <c r="N51" s="2" t="inlineStr">
-        <is>
-          <t>3,34%</t>
-        </is>
-      </c>
-      <c r="O51" s="2" t="inlineStr">
-        <is>
-          <t>2,73%</t>
-        </is>
-      </c>
-      <c r="P51" s="2" t="inlineStr">
-        <is>
-          <t>3,84%</t>
-        </is>
-      </c>
-      <c r="Q51" s="2" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="R51" s="2" t="inlineStr">
-        <is>
-          <t>219096</t>
-        </is>
-      </c>
-      <c r="S51" s="2" t="inlineStr">
-        <is>
-          <t>187029</t>
-        </is>
-      </c>
-      <c r="T51" s="2" t="inlineStr">
-        <is>
-          <t>251003</t>
-        </is>
-      </c>
-      <c r="U51" s="2" t="inlineStr">
-        <is>
-          <t>3,06%</t>
-        </is>
-      </c>
-      <c r="V51" s="2" t="inlineStr">
-        <is>
-          <t>2,61%</t>
-        </is>
-      </c>
-      <c r="W51" s="2" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="1" t="n"/>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>Otra persona que no reside en el hogar y que sí cobra aunque no de los ingresos del hogar</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>57508</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>43611</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>75307</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>2,18%</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>82512</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="inlineStr">
-        <is>
-          <t>67168</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr">
-        <is>
-          <t>97876</t>
-        </is>
-      </c>
-      <c r="N52" s="2" t="inlineStr">
-        <is>
-          <t>2,22%</t>
-        </is>
-      </c>
-      <c r="O52" s="2" t="inlineStr">
-        <is>
-          <t>1,81%</t>
-        </is>
-      </c>
-      <c r="P52" s="2" t="inlineStr">
-        <is>
-          <t>2,64%</t>
-        </is>
-      </c>
-      <c r="Q52" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="R52" s="2" t="inlineStr">
-        <is>
-          <t>140020</t>
-        </is>
-      </c>
-      <c r="S52" s="2" t="inlineStr">
-        <is>
-          <t>119339</t>
-        </is>
-      </c>
-      <c r="T52" s="2" t="inlineStr">
-        <is>
-          <t>164653</t>
-        </is>
-      </c>
-      <c r="U52" s="2" t="inlineStr">
-        <is>
-          <t>1,95%</t>
-        </is>
-      </c>
-      <c r="V52" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
-      <c r="W52" s="2" t="inlineStr">
-        <is>
-          <t>2,3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="1" t="n"/>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>Otra situación</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>277420</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>31256</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>978272</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>8,02%</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>28,28%</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>26594</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr">
-        <is>
-          <t>17307</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr">
-        <is>
-          <t>39657</t>
-        </is>
-      </c>
-      <c r="N53" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
-      <c r="O53" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="P53" s="2" t="inlineStr">
-        <is>
-          <t>1,07%</t>
-        </is>
-      </c>
-      <c r="Q53" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="R53" s="2" t="inlineStr">
-        <is>
-          <t>304014</t>
-        </is>
-      </c>
-      <c r="S53" s="2" t="inlineStr">
-        <is>
-          <t>55157</t>
-        </is>
-      </c>
-      <c r="T53" s="2" t="inlineStr">
-        <is>
-          <t>1192331</t>
-        </is>
-      </c>
-      <c r="U53" s="2" t="inlineStr">
-        <is>
-          <t>4,24%</t>
-        </is>
-      </c>
-      <c r="V53" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
-      <c r="W53" s="2" t="inlineStr">
-        <is>
-          <t>16,63%</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A39" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
@@ -6387,14 +4692,14 @@
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="J1:P1"/>
-    <mergeCell ref="A44:A53"/>
-    <mergeCell ref="A24:A33"/>
-    <mergeCell ref="A34:A43"/>
-    <mergeCell ref="A4:A13"/>
+    <mergeCell ref="A32:A38"/>
+    <mergeCell ref="A4:A10"/>
+    <mergeCell ref="A25:A31"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A14:A23"/>
     <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
+    <mergeCell ref="A18:A24"/>
+    <mergeCell ref="A11:A17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/trans_orig/P3A$yo-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P3A$yo-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>401782</t>
+          <t>432141</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>371840</t>
+          <t>404275</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>428157</t>
+          <t>458547</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>63,28%</t>
+          <t>62,61%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>58,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>67,43%</t>
+          <t>66,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>680879</t>
+          <t>685471</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>666884</t>
+          <t>669777</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>692062</t>
+          <t>695963</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1082661</t>
+          <t>1117612</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1043492</t>
+          <t>1078691</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1118120</t>
+          <t>1148761</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>78,46%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>76,71%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>80,65%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>289092</t>
+          <t>325098</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>260394</t>
+          <t>296891</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>318264</t>
+          <t>353767</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>47,1%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>152102</t>
+          <t>161405</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>118851</t>
+          <t>144608</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>171940</t>
+          <t>180408</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>441194</t>
+          <t>486503</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>380843</t>
+          <t>451802</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>480453</t>
+          <t>518767</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>36,42%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>165961</t>
+          <t>170415</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>140079</t>
+          <t>146844</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>199580</t>
+          <t>201531</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>200082</t>
+          <t>164761</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>156112</t>
+          <t>144399</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>312227</t>
+          <t>186102</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>366043</t>
+          <t>335176</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>313766</t>
+          <t>301422</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>498509</t>
+          <t>373035</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>26,19%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>31708</t>
+          <t>32843</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23464</t>
+          <t>23511</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41767</t>
+          <t>43645</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>35315</t>
+          <t>36907</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26694</t>
+          <t>29310</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44214</t>
+          <t>45845</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>67024</t>
+          <t>69750</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>53805</t>
+          <t>59149</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>79050</t>
+          <t>84167</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>21042</t>
+          <t>22425</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14090</t>
+          <t>15079</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>29883</t>
+          <t>32063</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>23445</t>
+          <t>26279</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>16604</t>
+          <t>20007</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>31261</t>
+          <t>35047</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>44486</t>
+          <t>48704</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>34936</t>
+          <t>38787</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>57067</t>
+          <t>61241</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -1290,32 +1290,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19695</t>
+          <t>20459</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13185</t>
+          <t>13727</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>28375</t>
+          <t>30269</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1325,32 +1325,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25311</t>
+          <t>26571</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18468</t>
+          <t>20503</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>32182</t>
+          <t>33491</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>45006</t>
+          <t>47030</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>35831</t>
+          <t>37182</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>55863</t>
+          <t>59036</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1465</t>
+          <t>2120</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1413,12 +1413,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7853</t>
+          <t>8010</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>397</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1774</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1473,32 +1473,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1844</t>
+          <t>2518</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>402</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8291</t>
+          <t>7590</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,01%</t>
+          <t>0,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,53%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>619109</t>
+          <t>681901</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>296623</t>
+          <t>644439</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>791176</t>
+          <t>716147</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>51,9%</t>
+          <t>65,01%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>61,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,33%</t>
+          <t>68,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>883438</t>
+          <t>985056</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>865503</t>
+          <t>963321</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>898428</t>
+          <t>1002231</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1502548</t>
+          <t>1666957</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1017286</t>
+          <t>1624680</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1708633</t>
+          <t>1706175</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>69,84%</t>
+          <t>78,62%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>80,47%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>473828</t>
+          <t>534023</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>237376</t>
+          <t>494795</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>609670</t>
+          <t>568768</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>50,91%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>51,11%</t>
+          <t>54,22%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>239285</t>
+          <t>258177</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>217128</t>
+          <t>232701</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>262583</t>
+          <t>281594</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>713113</t>
+          <t>792200</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>478250</t>
+          <t>748190</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>816366</t>
+          <t>839179</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>39,58%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>271931</t>
+          <t>291613</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>133360</t>
+          <t>258387</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>358109</t>
+          <t>327868</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>244987</t>
+          <t>275946</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>220884</t>
+          <t>248298</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>271239</t>
+          <t>306308</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>516918</t>
+          <t>567559</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>338625</t>
+          <t>522065</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>599304</t>
+          <t>613284</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>28,92%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>28431</t>
+          <t>30240</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14727</t>
+          <t>21944</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>41613</t>
+          <t>40809</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>43839</t>
+          <t>47427</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>34542</t>
+          <t>37846</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>54215</t>
+          <t>56808</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>72271</t>
+          <t>77667</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>47881</t>
+          <t>64079</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>88892</t>
+          <t>90495</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -1972,32 +1972,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>19973</t>
+          <t>23240</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9046</t>
+          <t>14038</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>35732</t>
+          <t>36225</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2007,32 +2007,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>26954</t>
+          <t>30166</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>19848</t>
+          <t>22617</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>35752</t>
+          <t>39606</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>46927</t>
+          <t>53407</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>30599</t>
+          <t>41330</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>63357</t>
+          <t>69171</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -2085,32 +2085,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>17022</t>
+          <t>18362</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8318</t>
+          <t>11213</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28359</t>
+          <t>33987</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2120,32 +2120,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>25699</t>
+          <t>27370</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18826</t>
+          <t>20231</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>34290</t>
+          <t>36788</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>42722</t>
+          <t>45732</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>27551</t>
+          <t>34976</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>55928</t>
+          <t>61412</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -2198,32 +2198,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>255764</t>
+          <t>13308</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10760</t>
+          <t>7612</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>736657</t>
+          <t>23902</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2233,32 +2233,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7281</t>
+          <t>8291</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3546</t>
+          <t>3739</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14347</t>
+          <t>15728</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2268,32 +2268,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>263046</t>
+          <t>21599</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>17481</t>
+          <t>13759</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>859721</t>
+          <t>32448</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>477663</t>
+          <t>542863</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>447112</t>
+          <t>511170</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>507257</t>
+          <t>572086</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>67,6%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>63,45%</t>
+          <t>63,65%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>71,24%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>870118</t>
+          <t>736714</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>842797</t>
+          <t>714114</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>904586</t>
+          <t>754309</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1347781</t>
+          <t>1279576</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1289041</t>
+          <t>1235786</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1445410</t>
+          <t>1317392</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>79,21%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>76,5%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>81,56%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>354950</t>
+          <t>410497</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>325665</t>
+          <t>376273</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>387721</t>
+          <t>442725</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>50,37%</t>
+          <t>51,12%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>55,02%</t>
+          <t>55,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>173422</t>
+          <t>195711</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>88730</t>
+          <t>174042</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>232674</t>
+          <t>219005</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>528372</t>
+          <t>606208</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>359697</t>
+          <t>565089</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>622696</t>
+          <t>643033</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>39,81%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>223641</t>
+          <t>246018</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>194309</t>
+          <t>216625</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>259888</t>
+          <t>281750</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>195372</t>
+          <t>226753</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>92286</t>
+          <t>202167</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>264913</t>
+          <t>255496</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>419013</t>
+          <t>472771</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>277478</t>
+          <t>433905</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>497298</t>
+          <t>516034</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>31,95%</t>
         </is>
       </c>
     </row>
@@ -2654,22 +2654,22 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>16890</t>
+          <t>18716</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10473</t>
+          <t>11985</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>26668</t>
+          <t>29201</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2689,32 +2689,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>34121</t>
+          <t>38424</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>16121</t>
+          <t>29762</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>48787</t>
+          <t>49522</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
+          <t>4,73%</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
           <t>3,66%</t>
         </is>
       </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>1,73%</t>
-        </is>
-      </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2724,32 +2724,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>51011</t>
+          <t>57140</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>32282</t>
+          <t>44831</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>65660</t>
+          <t>70761</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -2767,32 +2767,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>18225</t>
+          <t>21397</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10887</t>
+          <t>12539</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29511</t>
+          <t>33125</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2802,32 +2802,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>25085</t>
+          <t>29368</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10688</t>
+          <t>22067</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>36396</t>
+          <t>39211</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2837,32 +2837,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>43310</t>
+          <t>50765</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>27824</t>
+          <t>40005</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>57793</t>
+          <t>65449</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -2880,32 +2880,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>9085</t>
+          <t>10565</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4733</t>
+          <t>5533</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>15781</t>
+          <t>17511</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2915,32 +2915,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>10491</t>
+          <t>11609</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>4648</t>
+          <t>6890</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>17377</t>
+          <t>17989</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2950,32 +2950,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>19576</t>
+          <t>22174</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>11354</t>
+          <t>15065</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>29913</t>
+          <t>30286</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -2993,32 +2993,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3967</t>
+          <t>5514</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1167</t>
+          <t>1858</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9298</t>
+          <t>13304</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3028,32 +3028,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3988</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1032</t>
+          <t>3157</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>13615</t>
+          <t>19979</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3063,32 +3063,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>7955</t>
+          <t>13873</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3435</t>
+          <t>7439</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>17631</t>
+          <t>27028</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>622054</t>
+          <t>655652</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>588974</t>
+          <t>622570</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>652798</t>
+          <t>685474</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>66,26%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>63,59%</t>
+          <t>62,92%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>963142</t>
+          <t>978683</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>935813</t>
+          <t>955018</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>990670</t>
+          <t>1001245</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>87,55%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1585195</t>
+          <t>1634336</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1542309</t>
+          <t>1591504</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1643001</t>
+          <t>1671898</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>78,48%</t>
+          <t>77,56%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>81,34%</t>
+          <t>79,34%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>437081</t>
+          <t>468500</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>405121</t>
+          <t>435428</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>471841</t>
+          <t>503136</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>47,35%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>50,94%</t>
+          <t>50,85%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>200961</t>
+          <t>216045</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>161415</t>
+          <t>194287</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>227891</t>
+          <t>239097</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>638042</t>
+          <t>684546</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>562910</t>
+          <t>641048</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>682187</t>
+          <t>727176</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>34,51%</t>
         </is>
       </c>
     </row>
@@ -3336,32 +3336,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>248825</t>
+          <t>266089</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>213908</t>
+          <t>234232</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>278676</t>
+          <t>301725</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3371,32 +3371,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>262617</t>
+          <t>281462</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>209021</t>
+          <t>254814</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>296202</t>
+          <t>310450</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3406,32 +3406,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>511441</t>
+          <t>547551</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>446983</t>
+          <t>506173</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>560134</t>
+          <t>593982</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>28,19%</t>
         </is>
       </c>
     </row>
@@ -3449,32 +3449,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>28096</t>
+          <t>24950</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>18740</t>
+          <t>17255</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>49501</t>
+          <t>36986</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3484,67 +3484,67 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>33565</t>
+          <t>35880</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>25251</t>
+          <t>27375</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>43285</t>
+          <t>45227</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
+          <t>2,45%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>4,05%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>60830</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>48673</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>74803</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>2,89%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
           <t>2,31%</t>
         </is>
       </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>3,96%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>61660</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>49100</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>81914</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>3,05%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>2,43%</t>
-        </is>
-      </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -3562,32 +3562,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>35971</t>
+          <t>36864</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>25793</t>
+          <t>26745</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>49549</t>
+          <t>50696</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3597,32 +3597,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>48401</t>
+          <t>52059</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>36784</t>
+          <t>41404</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>62019</t>
+          <t>65330</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3632,32 +3632,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>84372</t>
+          <t>88923</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>69106</t>
+          <t>73564</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>103050</t>
+          <t>108028</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -3675,17 +3675,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>11705</t>
+          <t>12463</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6999</t>
+          <t>7523</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>18597</t>
+          <t>19568</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,7 +3700,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3710,32 +3710,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>21011</t>
+          <t>22968</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>14759</t>
+          <t>16354</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>29340</t>
+          <t>30925</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3745,32 +3745,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>32716</t>
+          <t>35432</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>24040</t>
+          <t>26775</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>42587</t>
+          <t>47045</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -3788,32 +3788,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>16224</t>
+          <t>16362</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>8433</t>
+          <t>8680</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>32885</t>
+          <t>29944</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3823,32 +3823,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>14946</t>
+          <t>16278</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>8761</t>
+          <t>8880</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>28513</t>
+          <t>25661</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3858,32 +3858,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>31170</t>
+          <t>32640</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>19483</t>
+          <t>19478</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>47112</t>
+          <t>46368</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>2120608</t>
+          <t>2312557</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1616269</t>
+          <t>2251481</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2302431</t>
+          <t>2374350</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>67,23%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>3397577</t>
+          <t>3385923</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3353826</t>
+          <t>3345644</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3455773</t>
+          <t>3421280</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>5518185</t>
+          <t>5698481</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>4883769</t>
+          <t>5618246</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5758566</t>
+          <t>5775071</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>78,41%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>68,12%</t>
+          <t>77,31%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>79,47%</t>
         </is>
       </c>
     </row>
@@ -4018,32 +4018,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>1554951</t>
+          <t>1738118</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1192592</t>
+          <t>1665820</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1700703</t>
+          <t>1796052</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>49,22%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>50,86%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4053,32 +4053,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>765770</t>
+          <t>831338</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>614292</t>
+          <t>786819</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>843229</t>
+          <t>873757</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4088,32 +4088,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>2320721</t>
+          <t>2569457</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>2016671</t>
+          <t>2485627</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>2492035</t>
+          <t>2654563</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>36,53%</t>
         </is>
       </c>
     </row>
@@ -4131,32 +4131,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>910358</t>
+          <t>974134</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>712530</t>
+          <t>911085</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1001359</t>
+          <t>1044348</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4166,32 +4166,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>903057</t>
+          <t>948922</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>737230</t>
+          <t>897206</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1025692</t>
+          <t>1004927</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4201,32 +4201,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>1813415</t>
+          <t>1923057</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1611652</t>
+          <t>1834414</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1974983</t>
+          <t>2009994</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,66%</t>
         </is>
       </c>
     </row>
@@ -4244,32 +4244,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>105125</t>
+          <t>106749</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>79067</t>
+          <t>88936</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>129235</t>
+          <t>127027</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4279,32 +4279,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>146841</t>
+          <t>158638</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>117353</t>
+          <t>140113</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>167125</t>
+          <t>177963</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4314,32 +4314,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>251965</t>
+          <t>265387</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>209298</t>
+          <t>241658</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>283026</t>
+          <t>293041</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -4357,32 +4357,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>95211</t>
+          <t>103927</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>72969</t>
+          <t>85939</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>117979</t>
+          <t>127884</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4392,32 +4392,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>123885</t>
+          <t>137872</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>99331</t>
+          <t>118070</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>143985</t>
+          <t>156332</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4427,32 +4427,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>219096</t>
+          <t>241799</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>186252</t>
+          <t>215168</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>253087</t>
+          <t>268184</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -4470,32 +4470,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>57508</t>
+          <t>61849</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>42948</t>
+          <t>49532</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>74293</t>
+          <t>79977</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4505,32 +4505,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>82512</t>
+          <t>88518</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>67461</t>
+          <t>76532</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>98508</t>
+          <t>104053</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4540,32 +4540,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>140020</t>
+          <t>150367</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>118415</t>
+          <t>130647</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>162345</t>
+          <t>170365</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -4583,32 +4583,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>277420</t>
+          <t>37304</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>30528</t>
+          <t>26808</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>1057929</t>
+          <t>54994</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4618,32 +4618,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>26594</t>
+          <t>33324</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>16841</t>
+          <t>22608</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>40858</t>
+          <t>47478</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4653,32 +4653,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>304014</t>
+          <t>70628</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>54832</t>
+          <t>54393</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1050624</t>
+          <t>92180</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
